--- a/Luban/Excel/杂录.xlsx
+++ b/Luban/Excel/杂录.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="7247" windowHeight="1428"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="琐碎思路" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>战斗流派</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>百姓的委托：除掉</t>
-  </si>
-  <si>
-    <t>魂落真诀</t>
   </si>
   <si>
     <t>强盗的战前招呼</t>
@@ -1140,7 +1137,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:S26"/>
+  <dimension ref="B2:S25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="10" max="10" width="11.4444444444444" customWidth="1"/>
@@ -1357,11 +1354,6 @@
     <row r="25" spans="3:3">
       <c r="C25" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1384,7 +1376,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
